--- a/artfynd/S 2000-2023 artfynd.xlsx
+++ b/artfynd/S 2000-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1483,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>63586496</v>
+        <v>135304867</v>
       </c>
       <c r="B9" t="n">
-        <v>57950</v>
+        <v>80499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,48 +1494,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Valås,  Valebråta, Anten,, Vg</t>
+          <t>Angertuvan södra sluttning, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>345351</v>
+        <v>345417</v>
       </c>
       <c r="R9" t="n">
-        <v>6430442</v>
+        <v>6430460</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1559,22 +1551,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2017-02-15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2017-02-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,28 +1565,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Göran Andersson</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Andersson, Lars Andersson, Thomas Svensson</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>68245194</v>
+        <v>63586496</v>
       </c>
       <c r="B10" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,21 +1595,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1635,12 +1618,12 @@
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valås,  Valebråta, Anten,, Vg</t>
@@ -1677,27 +1660,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2017-11-06</t>
+          <t>2017-02-15</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2017-11-06</t>
+          <t>2017-02-15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>stöttes</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,39 +1695,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Andersson, Thomas Svensson</t>
+          <t>Göran Andersson, Lars Andersson, Thomas Svensson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>57169717</v>
+        <v>68245194</v>
       </c>
       <c r="B11" t="n">
-        <v>57794</v>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102621</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1758,7 +1736,11 @@
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1796,22 +1778,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2016-02-29</t>
+          <t>2017-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2017-11-06</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2016-02-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:15</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>stöttes</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,27 +1825,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>57181955</v>
+        <v>57169717</v>
       </c>
       <c r="B12" t="n">
-        <v>58327</v>
+        <v>57794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>102621</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1873,11 +1860,7 @@
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valås,  Valebråta, Anten,, Vg</t>
@@ -1914,22 +1897,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2016-03-01</t>
+          <t>2016-02-29</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2016-03-01</t>
+          <t>2016-02-29</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1956,42 +1939,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>61654755</v>
+        <v>57181955</v>
       </c>
       <c r="B13" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valås,  Valebråta, Anten,, Vg</t>
@@ -2028,17 +2015,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2016-10-05</t>
+          <t>2016-03-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2016-10-05</t>
+          <t>2016-03-01</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2063,49 +2050,49 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Göran Andersson, Thomas Svensson, Lars Andersson</t>
+          <t>Göran Andersson, Thomas Svensson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>68245186</v>
+        <v>61654755</v>
       </c>
       <c r="B14" t="n">
-        <v>58636</v>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valås,  Valebråta, Anten,, Vg</t>
@@ -2142,22 +2129,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2017-11-06</t>
+          <t>2016-10-05</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2017-11-06</t>
+          <t>2016-10-05</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2177,10 +2164,124 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
+          <t>Göran Andersson, Thomas Svensson, Lars Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>68245186</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Valås,  Valebråta, Anten,, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>345351</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6430442</v>
+      </c>
+      <c r="S15" t="n">
+        <v>100</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Långared</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2017-11-06</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2017-11-06</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Göran Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
           <t>Göran Andersson, Thomas Svensson</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 2000-2023 artfynd.xlsx
+++ b/artfynd/S 2000-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122009481</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122009296</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122009915</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61521434</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1238,6 +1263,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122009720</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1364,6 +1394,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122009256</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1480,6 +1515,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122009847</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1581,6 +1621,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135304867</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1699,6 +1744,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63586496</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1822,6 +1872,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68245194</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1936,6 +1991,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57169717</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2054,6 +2114,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57181955</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2168,6 +2233,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61654755</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2282,8 +2352,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68245186</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 2000-2023 artfynd.xlsx
+++ b/artfynd/S 2000-2023 artfynd.xlsx
@@ -1526,7 +1526,7 @@
         <v>135304867</v>
       </c>
       <c r="B9" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 2000-2023 artfynd.xlsx
+++ b/artfynd/S 2000-2023 artfynd.xlsx
@@ -1526,7 +1526,7 @@
         <v>135304867</v>
       </c>
       <c r="B9" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 2000-2023 artfynd.xlsx
+++ b/artfynd/S 2000-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1523,10 +1523,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>63586496</v>
+        <v>135304867</v>
       </c>
       <c r="B9" t="n">
-        <v>57950</v>
+        <v>80567</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,48 +1534,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Valås,  Valebråta, Anten,, Vg</t>
+          <t>Angertuvan södra sluttning, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>345351</v>
+        <v>345417</v>
       </c>
       <c r="R9" t="n">
-        <v>6430442</v>
+        <v>6430460</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1599,22 +1591,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2017-02-15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2017-02-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,33 +1605,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Göran Andersson</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Andersson, Lars Andersson, Thomas Svensson</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63586496</t>
+          <t>https://artportalen.se/Sighting/135304867</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>68245194</v>
+        <v>63586496</v>
       </c>
       <c r="B10" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,21 +1640,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1680,12 +1663,12 @@
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valås,  Valebråta, Anten,, Vg</t>
@@ -1722,27 +1705,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2017-11-06</t>
+          <t>2017-02-15</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2017-11-06</t>
+          <t>2017-02-15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>stöttes</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1762,44 +1740,44 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Andersson, Thomas Svensson</t>
+          <t>Göran Andersson, Lars Andersson, Thomas Svensson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68245194</t>
+          <t>https://artportalen.se/Sighting/63586496</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>57169717</v>
+        <v>68245194</v>
       </c>
       <c r="B11" t="n">
-        <v>57794</v>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102621</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1808,7 +1786,11 @@
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1846,22 +1828,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2016-02-29</t>
+          <t>2017-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2017-11-06</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2016-02-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:15</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>stöttes</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,33 +1874,33 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/57169717</t>
+          <t>https://artportalen.se/Sighting/68245194</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>57181955</v>
+        <v>57169717</v>
       </c>
       <c r="B12" t="n">
-        <v>58327</v>
+        <v>57794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>102621</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1928,11 +1915,7 @@
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valås,  Valebråta, Anten,, Vg</t>
@@ -1969,22 +1952,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2016-03-01</t>
+          <t>2016-02-29</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2016-03-01</t>
+          <t>2016-02-29</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2010,48 +1993,52 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/57181955</t>
+          <t>https://artportalen.se/Sighting/57169717</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>61654755</v>
+        <v>57181955</v>
       </c>
       <c r="B13" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valås,  Valebråta, Anten,, Vg</t>
@@ -2088,17 +2075,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2016-10-05</t>
+          <t>2016-03-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2016-10-05</t>
+          <t>2016-03-01</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2123,54 +2110,54 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Göran Andersson, Thomas Svensson, Lars Andersson</t>
+          <t>Göran Andersson, Thomas Svensson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61654755</t>
+          <t>https://artportalen.se/Sighting/57181955</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>68245186</v>
+        <v>61654755</v>
       </c>
       <c r="B14" t="n">
-        <v>58636</v>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valås,  Valebråta, Anten,, Vg</t>
@@ -2207,22 +2194,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2017-11-06</t>
+          <t>2016-10-05</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2017-11-06</t>
+          <t>2016-10-05</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2242,11 +2229,130 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Göran Andersson, Thomas Svensson</t>
+          <t>Göran Andersson, Thomas Svensson, Lars Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61654755</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>68245186</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Valås,  Valebråta, Anten,, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>345351</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6430442</v>
+      </c>
+      <c r="S15" t="n">
+        <v>100</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Långared</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2017-11-06</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2017-11-06</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Göran Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Göran Andersson, Thomas Svensson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/68245186</t>
         </is>
@@ -2267,6 +2373,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
